--- a/data/skillLevel.xlsx
+++ b/data/skillLevel.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="skillLevel" sheetId="1" r:id="rId1"/>
@@ -1245,6 +1250,15 @@
   <sheetPr/>
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="19.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="24.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="29.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="24.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="28.5555555555556" customWidth="1"/>
+    <col min="10" max="10" width="31.3333333333333" customWidth="1"/>
+    <col min="11" max="11" width="26.1111111111111" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">

--- a/data/skillLevel.xlsx
+++ b/data/skillLevel.xlsx
@@ -94,7 +94,7 @@
     <t>0(默认值)</t>
   </si>
   <si>
-    <t>atk</t>
+    <t>base_attack</t>
   </si>
   <si>
     <t>bulletCount</t>

--- a/data/skillLevel.xlsx
+++ b/data/skillLevel.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="19200" windowHeight="7215"/>
   </bookViews>
   <sheets>
     <sheet name="skillLevel" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -104,6 +104,24 @@
   </si>
   <si>
     <t>ricochetCount</t>
+  </si>
+  <si>
+    <t>base_attack_speed</t>
+  </si>
+  <si>
+    <t>base_crit_rate</t>
+  </si>
+  <si>
+    <t>base_crit_dmg</t>
+  </si>
+  <si>
+    <t>round_time</t>
+  </si>
+  <si>
+    <t>spawn_interval</t>
+  </si>
+  <si>
+    <t>spawn_per_wave</t>
   </si>
 </sst>
 </file>
@@ -1248,16 +1266,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="19.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="12.625"/>
+    <col min="2" max="2" width="19.5583333333333" customWidth="1"/>
     <col min="3" max="3" width="24.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="29.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="24.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="28.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="29.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="24.225" customWidth="1"/>
+    <col min="9" max="9" width="28.5583333333333" customWidth="1"/>
     <col min="10" max="10" width="31.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="26.1111111111111" customWidth="1"/>
+    <col min="11" max="11" width="26.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1395,7 +1414,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1406,13 +1425,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1423,13 +1442,13 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1440,13 +1459,13 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1457,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -1474,13 +1493,13 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1491,13 +1510,13 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1545,7 +1564,7 @@
         <v>23</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1562,7 +1581,568 @@
         <v>23</v>
       </c>
       <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
         <v>1</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>300</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>400</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>700</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>1100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>1800</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>2900</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>4700</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>7600</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26">
+        <v>12300</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>300</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>800</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>6</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>2000</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>4000</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>6</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>500</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>2000</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>5000</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>8000</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>12000</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>200</v>
+      </c>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>500</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>1500</v>
+      </c>
+      <c r="D39" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" ht="12" customHeight="1" spans="1:5">
+      <c r="A40">
+        <v>9</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>200</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>1000</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>2500</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>9</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>3500</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>4500</v>
+      </c>
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>10</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>200</v>
+      </c>
+      <c r="D45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>10</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>1500</v>
+      </c>
+      <c r="D46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>10</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>3500</v>
+      </c>
+      <c r="D47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>10</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>6000</v>
+      </c>
+      <c r="D48" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>10</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49">
+        <v>10000</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/skillLevel.xlsx
+++ b/data/skillLevel.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7215"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="skillLevel" sheetId="1" r:id="rId1"/>
@@ -1267,16 +1267,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.625"/>
-    <col min="2" max="2" width="19.5583333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.6296296296296"/>
+    <col min="2" max="2" width="19.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="24.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="29.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="24.225" customWidth="1"/>
-    <col min="9" max="9" width="28.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="29.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="24.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="27.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="28.5555555555556" customWidth="1"/>
     <col min="10" max="10" width="31.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="26.1083333333333" customWidth="1"/>
+    <col min="11" max="11" width="26.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">

--- a/data/skillLevel.xlsx
+++ b/data/skillLevel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
   <si>
     <t>Id</t>
   </si>
@@ -40,6 +40,9 @@
     <t>skillLevel</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>upCost</t>
   </si>
   <si>
@@ -61,24 +64,33 @@
     <t>attrValue3</t>
   </si>
   <si>
+    <t>changeAttr4</t>
+  </si>
+  <si>
+    <t>attrValue4</t>
+  </si>
+  <si>
     <t>specialEffect</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>技能id</t>
   </si>
   <si>
     <t>技能等级</t>
   </si>
   <si>
+    <t>技能描述</t>
+  </si>
+  <si>
     <t>解锁消耗</t>
   </si>
   <si>
@@ -88,40 +100,334 @@
     <t>每级改变的属性值</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>改变的属性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>属性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加值</t>
+    </r>
+  </si>
+  <si>
     <t>特殊效果key（如解锁功能）</t>
   </si>
   <si>
     <t>0(默认值)</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点攻击伤害</t>
+    </r>
+  </si>
+  <si>
     <t>base_attack</t>
   </si>
   <si>
+    <t>提升2点攻击伤害</t>
+  </si>
+  <si>
+    <t>提升5点攻击伤害</t>
+  </si>
+  <si>
+    <t>提升7点攻击伤害</t>
+  </si>
+  <si>
+    <t>提升9点攻击伤害</t>
+  </si>
+  <si>
+    <t>攻击弹道+1</t>
+  </si>
+  <si>
     <t>bulletCount</t>
   </si>
   <si>
+    <t>攻击弹道+2</t>
+  </si>
+  <si>
+    <t>攻击弹道+3</t>
+  </si>
+  <si>
+    <t>解锁超级子弹</t>
+  </si>
+  <si>
     <t>UnlockSuperBullet</t>
   </si>
   <si>
+    <t>子弹击中边界后能够弹射1次</t>
+  </si>
+  <si>
     <t>ricochetCount</t>
   </si>
   <si>
+    <t>子弹击中边界后能够弹射2次</t>
+  </si>
+  <si>
+    <t>子弹击中边界后能够弹射3次</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.1</t>
+  </si>
+  <si>
     <t>base_attack_speed</t>
   </si>
   <si>
+    <t>增加攻击速度0.2</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.3</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.4</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.5</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.6</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.7</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.8</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.9</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.10</t>
+  </si>
+  <si>
+    <t>增加暴击几率10%</t>
+  </si>
+  <si>
     <t>base_crit_rate</t>
   </si>
   <si>
+    <t>增加暴击几率15%</t>
+  </si>
+  <si>
+    <t>增加暴击几率20%</t>
+  </si>
+  <si>
+    <t>增加暴击几率25%</t>
+  </si>
+  <si>
+    <t>增加暴击几率30%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害50%</t>
+  </si>
+  <si>
     <t>base_crit_dmg</t>
   </si>
   <si>
+    <t>增加暴击伤害70%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害90%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害120%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害150%</t>
+  </si>
+  <si>
+    <r>
+      <t>增加对局使劲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10s</t>
+    </r>
+  </si>
+  <si>
     <t>round_time</t>
   </si>
   <si>
+    <r>
+      <t>增加对局使劲2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0s</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>增加对局使劲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>30s</t>
+    </r>
+  </si>
+  <si>
+    <t>减少刷怪间隔0.1s</t>
+  </si>
+  <si>
     <t>spawn_interval</t>
   </si>
   <si>
+    <t>减少刷怪间隔0.2s</t>
+  </si>
+  <si>
+    <t>减少刷怪间隔0.4s</t>
+  </si>
+  <si>
+    <t>减少刷怪间隔0.6s</t>
+  </si>
+  <si>
+    <t>减少刷怪间隔1s</t>
+  </si>
+  <si>
+    <r>
+      <t>提升没波出怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>只</t>
+    </r>
+  </si>
+  <si>
     <t>spawn_per_wave</t>
+  </si>
+  <si>
+    <t>提升没波出怪2只</t>
+  </si>
+  <si>
+    <r>
+      <t>提升没波出怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>只</t>
+    </r>
+  </si>
+  <si>
+    <t>提升没波出怪4只</t>
+  </si>
+  <si>
+    <r>
+      <t>提升没波出怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>只</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -134,13 +440,23 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -286,6 +602,18 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5B4B00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5B4B00"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -588,7 +916,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -607,142 +935,151 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -792,6 +1129,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1266,21 +1604,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6296296296296"/>
     <col min="2" max="2" width="19.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="24.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="29.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="24.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="27.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="28.5555555555556" customWidth="1"/>
-    <col min="10" max="10" width="31.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="26.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="69.8888888888889" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="29.5555555555556" customWidth="1"/>
+    <col min="6" max="6" width="24.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="27.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="27.2222222222222" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="24.4444444444444" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20" style="1" customWidth="1"/>
+    <col min="13" max="13" width="31.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="26.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1311,838 +1654,1055 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="C4"/>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5">
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
         <v>500</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7">
         <v>2000</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7">
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8">
         <v>5000</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8">
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9">
         <v>10000</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>2</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
         <v>200</v>
       </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10">
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11">
         <v>500</v>
       </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11">
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
         <v>1200</v>
       </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12">
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
         <v>1000</v>
       </c>
-      <c r="J13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14">
         <v>800</v>
       </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14">
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>4</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15">
         <v>1600</v>
       </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15">
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>4</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16">
         <v>2400</v>
       </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16">
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="K16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>5</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17">
         <v>100</v>
       </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18">
         <v>300</v>
       </c>
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>5</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19">
         <v>400</v>
       </c>
-      <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>5</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20">
         <v>700</v>
       </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>5</v>
       </c>
       <c r="B21">
         <v>5</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21">
         <v>1100</v>
       </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>5</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22">
         <v>1800</v>
       </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="E22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>5</v>
       </c>
       <c r="B23">
         <v>7</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23">
         <v>2900</v>
       </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="E23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>5</v>
       </c>
       <c r="B24">
         <v>8</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24">
         <v>4700</v>
       </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>5</v>
       </c>
       <c r="B25">
         <v>9</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25">
         <v>7600</v>
       </c>
-      <c r="D25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>5</v>
       </c>
       <c r="B26">
         <v>10</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26">
         <v>12300</v>
       </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="E26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>6</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27">
         <v>300</v>
       </c>
-      <c r="D27" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27">
+      <c r="E27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27">
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>6</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28">
         <v>800</v>
       </c>
-      <c r="D28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28">
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28">
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>6</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29">
         <v>2000</v>
       </c>
-      <c r="D29" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29">
+      <c r="E29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29">
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>6</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30">
         <v>4000</v>
       </c>
-      <c r="D30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30">
+      <c r="E30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30">
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>6</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31">
         <v>10000</v>
       </c>
-      <c r="D31" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31">
+      <c r="E31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31">
         <v>0.3</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>7</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32">
         <v>500</v>
       </c>
-      <c r="D32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>7</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33">
         <v>2000</v>
       </c>
-      <c r="D33" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="E33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>7</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34">
         <v>5000</v>
       </c>
-      <c r="D34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="E34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>7</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35">
         <v>8000</v>
       </c>
-      <c r="D35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>7</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36">
         <v>12000</v>
       </c>
-      <c r="D36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="E36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>8</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37">
         <v>200</v>
       </c>
-      <c r="D37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37">
+      <c r="E37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>8</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38">
         <v>500</v>
       </c>
-      <c r="D38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38">
+      <c r="E38" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>8</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39">
         <v>1500</v>
       </c>
-      <c r="D39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39">
+      <c r="E39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39">
         <v>30</v>
       </c>
     </row>
-    <row r="40" ht="12" customHeight="1" spans="1:5">
+    <row r="40" ht="12" customHeight="1" spans="1:6">
       <c r="A40">
         <v>9</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40">
         <v>200</v>
       </c>
-      <c r="D40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40">
+      <c r="E40" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>9</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41">
         <v>1000</v>
       </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41">
+      <c r="E41" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>9</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42">
         <v>2500</v>
       </c>
-      <c r="D42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42">
+      <c r="E42" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42">
         <v>-0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>9</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43">
         <v>3500</v>
       </c>
-      <c r="D43" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43">
+      <c r="E43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>9</v>
       </c>
       <c r="B44">
         <v>5</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44">
         <v>4500</v>
       </c>
-      <c r="D44" t="s">
-        <v>28</v>
-      </c>
-      <c r="E44">
+      <c r="E44" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44">
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>10</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45">
         <v>200</v>
       </c>
-      <c r="D45" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45">
+      <c r="E45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>10</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46">
         <v>1500</v>
       </c>
-      <c r="D46" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46">
+      <c r="E46" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>10</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47">
         <v>3500</v>
       </c>
-      <c r="D47" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47">
+      <c r="E47" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>10</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48">
         <v>6000</v>
       </c>
-      <c r="D48" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48">
+      <c r="E48" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>10</v>
       </c>
       <c r="B49">
         <v>5</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49">
         <v>10000</v>
       </c>
-      <c r="D49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49">
+      <c r="E49" t="s">
+        <v>77</v>
+      </c>
+      <c r="F49">
         <v>5</v>
       </c>
     </row>

--- a/data/skillLevel.xlsx
+++ b/data/skillLevel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="83">
   <si>
     <t>Id</t>
   </si>
@@ -158,147 +158,129 @@
     <t/>
   </si>
   <si>
+    <t>攻击伤害+1</t>
+  </si>
+  <si>
+    <t>base_attack</t>
+  </si>
+  <si>
+    <t>攻击伤害+2</t>
+  </si>
+  <si>
+    <t>攻击伤害+5</t>
+  </si>
+  <si>
+    <t>攻击伤害+7</t>
+  </si>
+  <si>
+    <t>攻击伤害+9</t>
+  </si>
+  <si>
+    <t>攻击弹道+1</t>
+  </si>
+  <si>
+    <t>bulletCount</t>
+  </si>
+  <si>
+    <t>攻击弹道+2</t>
+  </si>
+  <si>
+    <t>攻击弹道+3</t>
+  </si>
+  <si>
+    <t>解锁超级子弹</t>
+  </si>
+  <si>
+    <t>UnlockSuperBullet</t>
+  </si>
+  <si>
+    <t>子弹击中边界后能够弹射1次</t>
+  </si>
+  <si>
+    <t>ricochetCount</t>
+  </si>
+  <si>
+    <t>子弹击中边界后能够弹射2次</t>
+  </si>
+  <si>
+    <t>子弹击中边界后能够弹射3次</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.1</t>
+  </si>
+  <si>
+    <t>base_attack_speed</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.2</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.3</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.4</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.5</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.6</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.7</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.8</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.9</t>
+  </si>
+  <si>
+    <t>增加攻击速度0.10</t>
+  </si>
+  <si>
+    <t>增加暴击几率10%</t>
+  </si>
+  <si>
+    <t>base_crit_rate</t>
+  </si>
+  <si>
+    <t>增加暴击几率15%</t>
+  </si>
+  <si>
+    <t>增加暴击几率20%</t>
+  </si>
+  <si>
+    <t>增加暴击几率25%</t>
+  </si>
+  <si>
+    <t>增加暴击几率30%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害50%</t>
+  </si>
+  <si>
+    <t>base_crit_dmg</t>
+  </si>
+  <si>
+    <t>增加暴击伤害70%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害90%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害120%</t>
+  </si>
+  <si>
+    <t>增加暴击伤害150%</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>提升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点攻击伤害</t>
-    </r>
-  </si>
-  <si>
-    <t>base_attack</t>
-  </si>
-  <si>
-    <t>提升2点攻击伤害</t>
-  </si>
-  <si>
-    <t>提升5点攻击伤害</t>
-  </si>
-  <si>
-    <t>提升7点攻击伤害</t>
-  </si>
-  <si>
-    <t>提升9点攻击伤害</t>
-  </si>
-  <si>
-    <t>攻击弹道+1</t>
-  </si>
-  <si>
-    <t>bulletCount</t>
-  </si>
-  <si>
-    <t>攻击弹道+2</t>
-  </si>
-  <si>
-    <t>攻击弹道+3</t>
-  </si>
-  <si>
-    <t>解锁超级子弹</t>
-  </si>
-  <si>
-    <t>UnlockSuperBullet</t>
-  </si>
-  <si>
-    <t>子弹击中边界后能够弹射1次</t>
-  </si>
-  <si>
-    <t>ricochetCount</t>
-  </si>
-  <si>
-    <t>子弹击中边界后能够弹射2次</t>
-  </si>
-  <si>
-    <t>子弹击中边界后能够弹射3次</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.1</t>
-  </si>
-  <si>
-    <t>base_attack_speed</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.2</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.3</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.4</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.5</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.6</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.7</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.8</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.9</t>
-  </si>
-  <si>
-    <t>增加攻击速度0.10</t>
-  </si>
-  <si>
-    <t>增加暴击几率10%</t>
-  </si>
-  <si>
-    <t>base_crit_rate</t>
-  </si>
-  <si>
-    <t>增加暴击几率15%</t>
-  </si>
-  <si>
-    <t>增加暴击几率20%</t>
-  </si>
-  <si>
-    <t>增加暴击几率25%</t>
-  </si>
-  <si>
-    <t>增加暴击几率30%</t>
-  </si>
-  <si>
-    <t>增加暴击伤害50%</t>
-  </si>
-  <si>
-    <t>base_crit_dmg</t>
-  </si>
-  <si>
-    <t>增加暴击伤害70%</t>
-  </si>
-  <si>
-    <t>增加暴击伤害90%</t>
-  </si>
-  <si>
-    <t>增加暴击伤害120%</t>
-  </si>
-  <si>
-    <t>增加暴击伤害150%</t>
-  </si>
-  <si>
-    <r>
       <t>增加对局使劲</t>
     </r>
     <r>
@@ -315,6 +297,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>增加对局使劲2</t>
     </r>
     <r>
@@ -328,6 +315,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>增加对局使劲</t>
     </r>
     <r>
@@ -340,7 +332,7 @@
     </r>
   </si>
   <si>
-    <t>减少刷怪间隔0.1s</t>
+    <t>减少刷怪间隔0.5s</t>
   </si>
   <si>
     <t>spawn_interval</t>
@@ -359,6 +351,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>提升没波出怪</t>
     </r>
     <r>
@@ -386,6 +383,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>提升没波出怪</t>
     </r>
     <r>
@@ -406,28 +408,13 @@
     </r>
   </si>
   <si>
-    <t>提升没波出怪4只</t>
-  </si>
-  <si>
-    <r>
-      <t>提升没波出怪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>只</t>
-    </r>
+    <t>攻击轮+1</t>
+  </si>
+  <si>
+    <t>burstCount</t>
+  </si>
+  <si>
+    <t>攻击轮+2</t>
   </si>
 </sst>
 </file>
@@ -1772,7 +1759,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -1796,13 +1783,13 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>26</v>
@@ -1826,7 +1813,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>26</v>
@@ -1850,7 +1837,7 @@
         <v>28</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>26</v>
@@ -1874,7 +1861,7 @@
         <v>28</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>26</v>
@@ -1892,7 +1879,7 @@
         <v>33</v>
       </c>
       <c r="D10">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
@@ -1916,13 +1903,13 @@
         <v>35</v>
       </c>
       <c r="D11">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>26</v>
@@ -1940,13 +1927,13 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>1200</v>
+        <v>8000</v>
       </c>
       <c r="E12" t="s">
         <v>34</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>26</v>
@@ -1985,7 +1972,7 @@
         <v>39</v>
       </c>
       <c r="D14">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
@@ -2009,13 +1996,13 @@
         <v>41</v>
       </c>
       <c r="D15">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>26</v>
@@ -2033,13 +2020,13 @@
         <v>42</v>
       </c>
       <c r="D16">
-        <v>2400</v>
+        <v>4000</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>26</v>
@@ -2083,7 +2070,7 @@
         <v>44</v>
       </c>
       <c r="F18">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2097,13 +2084,13 @@
         <v>46</v>
       </c>
       <c r="D19">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E19" t="s">
         <v>44</v>
       </c>
       <c r="F19">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2117,13 +2104,13 @@
         <v>47</v>
       </c>
       <c r="D20">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E20" t="s">
         <v>44</v>
       </c>
       <c r="F20">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2137,13 +2124,13 @@
         <v>48</v>
       </c>
       <c r="D21">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="E21" t="s">
         <v>44</v>
       </c>
       <c r="F21">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2157,13 +2144,13 @@
         <v>49</v>
       </c>
       <c r="D22">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
       </c>
       <c r="F22">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2177,13 +2164,13 @@
         <v>50</v>
       </c>
       <c r="D23">
-        <v>2900</v>
+        <v>8000</v>
       </c>
       <c r="E23" t="s">
         <v>44</v>
       </c>
       <c r="F23">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2197,13 +2184,13 @@
         <v>51</v>
       </c>
       <c r="D24">
-        <v>4700</v>
+        <v>16000</v>
       </c>
       <c r="E24" t="s">
         <v>44</v>
       </c>
       <c r="F24">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2217,13 +2204,13 @@
         <v>52</v>
       </c>
       <c r="D25">
-        <v>7600</v>
+        <v>32000</v>
       </c>
       <c r="E25" t="s">
         <v>44</v>
       </c>
       <c r="F25">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2237,7 +2224,7 @@
         <v>53</v>
       </c>
       <c r="D26">
-        <v>12300</v>
+        <v>50000</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
@@ -2257,7 +2244,7 @@
         <v>54</v>
       </c>
       <c r="D27">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
@@ -2277,13 +2264,13 @@
         <v>56</v>
       </c>
       <c r="D28">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E28" t="s">
         <v>55</v>
       </c>
       <c r="F28">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2297,13 +2284,13 @@
         <v>57</v>
       </c>
       <c r="D29">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E29" t="s">
         <v>55</v>
       </c>
       <c r="F29">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2317,13 +2304,13 @@
         <v>58</v>
       </c>
       <c r="D30">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="E30" t="s">
         <v>55</v>
       </c>
       <c r="F30">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2357,16 +2344,16 @@
         <v>60</v>
       </c>
       <c r="D32">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E32" t="s">
         <v>61</v>
       </c>
       <c r="F32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>7</v>
       </c>
@@ -2377,16 +2364,16 @@
         <v>62</v>
       </c>
       <c r="D33">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E33" t="s">
         <v>61</v>
       </c>
       <c r="F33">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>7</v>
       </c>
@@ -2397,7 +2384,7 @@
         <v>63</v>
       </c>
       <c r="D34">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E34" t="s">
         <v>61</v>
@@ -2406,7 +2393,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>7</v>
       </c>
@@ -2417,16 +2404,16 @@
         <v>64</v>
       </c>
       <c r="D35">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="E35" t="s">
         <v>61</v>
       </c>
       <c r="F35">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>7</v>
       </c>
@@ -2437,16 +2424,16 @@
         <v>65</v>
       </c>
       <c r="D36">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E36" t="s">
         <v>61</v>
       </c>
       <c r="F36">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>8</v>
       </c>
@@ -2457,7 +2444,7 @@
         <v>66</v>
       </c>
       <c r="D37">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E37" t="s">
         <v>67</v>
@@ -2466,7 +2453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>8</v>
       </c>
@@ -2477,16 +2464,16 @@
         <v>68</v>
       </c>
       <c r="D38">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E38" t="s">
         <v>67</v>
       </c>
       <c r="F38">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>8</v>
       </c>
@@ -2497,16 +2484,16 @@
         <v>69</v>
       </c>
       <c r="D39">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="E39" t="s">
         <v>67</v>
       </c>
       <c r="F39">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" ht="12" customHeight="1" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" ht="12" customHeight="1" spans="1:12">
       <c r="A40">
         <v>9</v>
       </c>
@@ -2517,16 +2504,16 @@
         <v>70</v>
       </c>
       <c r="D40">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
         <v>71</v>
       </c>
       <c r="F40">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>9</v>
       </c>
@@ -2537,7 +2524,7 @@
         <v>72</v>
       </c>
       <c r="D41">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E41" t="s">
         <v>71</v>
@@ -2546,7 +2533,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>9</v>
       </c>
@@ -2557,16 +2544,16 @@
         <v>73</v>
       </c>
       <c r="D42">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E42" t="s">
         <v>71</v>
       </c>
       <c r="F42">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>9</v>
       </c>
@@ -2577,16 +2564,16 @@
         <v>74</v>
       </c>
       <c r="D43">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="E43" t="s">
         <v>71</v>
       </c>
       <c r="F43">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>9</v>
       </c>
@@ -2597,16 +2584,16 @@
         <v>75</v>
       </c>
       <c r="D44">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="E44" t="s">
         <v>71</v>
       </c>
       <c r="F44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>10</v>
       </c>
@@ -2617,7 +2604,7 @@
         <v>76</v>
       </c>
       <c r="D45">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E45" t="s">
         <v>77</v>
@@ -2626,7 +2613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>10</v>
       </c>
@@ -2637,16 +2624,16 @@
         <v>78</v>
       </c>
       <c r="D46">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E46" t="s">
         <v>77</v>
       </c>
       <c r="F46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>10</v>
       </c>
@@ -2657,54 +2644,58 @@
         <v>79</v>
       </c>
       <c r="D47">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="E47" t="s">
         <v>77</v>
       </c>
       <c r="F47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:12">
       <c r="A48">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>80</v>
       </c>
       <c r="D48">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="E48" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F48">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" spans="1:12">
       <c r="A49">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49">
+        <v>5000</v>
+      </c>
+      <c r="E49" t="s">
         <v>81</v>
       </c>
-      <c r="D49">
-        <v>10000</v>
-      </c>
-      <c r="E49" t="s">
-        <v>77</v>
-      </c>
       <c r="F49">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
